--- a/cds_files/Arizona_CDS_2024-2025.xlsx
+++ b/cds_files/Arizona_CDS_2024-2025.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.19</v>
+        <v>0.63</v>
       </c>
       <c r="C3" t="n">
         <v>0.19</v>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="C4" t="n">
         <v>0.8100000000000001</v>
